--- a/output/pdf_financials_xlsx/TC.xlsx
+++ b/output/pdf_financials_xlsx/TC.xlsx
@@ -4677,7 +4677,7 @@
         <v>0.343</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0.784</v>
+        <v>1.632</v>
       </c>
       <c r="L91" s="3" t="n">
         <v>1.728</v>
@@ -4724,7 +4724,7 @@
         <v>2.764</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>8.106</v>
+        <v>25.785</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>14.072</v>

--- a/output/pdf_financials_xlsx/TC.xlsx
+++ b/output/pdf_financials_xlsx/TC.xlsx
@@ -793,40 +793,40 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>25.272221</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>29.758348</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>34.041699</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>38.007</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>57.439</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>67.446</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>71.437</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>78.568</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>7.059</v>
+        <v>86.066</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>7.095</v>
+        <v>109.91</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8.192</v>
+        <v>130.319</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>148.042</v>
       </c>
     </row>
     <row r="11">
@@ -869,7 +869,7 @@
         <v>-63.652</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>83.029</v>
+        <v>-65.01300000000001</v>
       </c>
     </row>
     <row r="12">
@@ -31566,7 +31566,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E347" s="5" t="n">

--- a/output/pdf_financials_xlsx/TC.xlsx
+++ b/output/pdf_financials_xlsx/TC.xlsx
@@ -1695,40 +1695,40 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.95991</v>
+        <v>1.80333</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.59662</v>
+        <v>1.522722</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.262726</v>
+        <v>1.667021</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.953</v>
+        <v>2.777</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>8.4</v>
+        <v>12.127</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>9.243</v>
+        <v>14.965</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>10.333</v>
+        <v>19.294</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>11.42</v>
+        <v>24.052</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>10.007</v>
+        <v>27.993</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>11.394</v>
+        <v>67.768</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>10.829</v>
+        <v>83.691</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>5.297</v>
+        <v>85.943</v>
       </c>
     </row>
     <row r="29">
@@ -1738,37 +1738,37 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>6.759713</v>
+        <v>7.603133</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>10.024945</v>
+        <v>10.951047</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>18.205683</v>
+        <v>19.609978</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>26.066</v>
+        <v>27.89</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>32.475</v>
+        <v>36.202</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>35.398</v>
+        <v>41.12</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>34.904</v>
+        <v>43.865</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>22.18</v>
+        <v>34.812</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>17.277</v>
+        <v>35.263</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-16.394</v>
+        <v>39.98</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>7.32</v>
+        <v>80.182</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>5.20238426466225</v>
+        <v>5.851493914214152</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>6.842559053314987</v>
+        <v>7.474673007495595</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>10.60400987544882</v>
+        <v>11.42194996855291</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>13.73202893282548</v>
+        <v>14.69294433117865</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>9.858205761017057</v>
+        <v>10.98958475628451</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>10.23025146454035</v>
+        <v>11.88394655692127</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>10.35281555413843</v>
+        <v>13.01072238947634</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>7.127203552676396</v>
+        <v>11.18630342992654</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>5.67693050795664</v>
+        <v>11.58682644568357</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-5.104906863630419</v>
+        <v>12.44932148395414</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>2.15714761431851</v>
+        <v>23.62901776110474</v>
       </c>
       <c r="M30" s="1" t="inlineStr">
         <is>
@@ -5033,40 +5033,40 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>1.80333</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>1.522722</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>1.667022</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>2.777</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>12.127</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>14.965</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>19.294</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>24.052</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>27.993</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>39.581</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>47.26</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="101">
@@ -5573,7 +5573,7 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
@@ -5582,7 +5582,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.542</v>
       </c>
     </row>
     <row r="113">
@@ -19916,7 +19916,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -20134,7 +20138,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -21240,7 +21244,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -21992,7 +22000,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E211" s="5" t="n">
         <v>0.8434199999999999</v>
       </c>
@@ -22182,7 +22194,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E214" s="5" t="n">
@@ -30700,7 +30712,11 @@
           <t>Network, depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -30772,7 +30788,11 @@
           <t>Network, amortization of intangible assets</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -31200,7 +31220,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
@@ -31338,7 +31362,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -32510,7 +32534,11 @@
           <t>Depreciation of property and equipment $</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -32862,7 +32890,11 @@
           <t>Network, depreciation of property and equipment (note 4)</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -32934,7 +32966,11 @@
           <t>Network, amortization of intangible assets (note 5)</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -33076,7 +33112,11 @@
           <t>Depreciation of property and equipment (note 4)</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
           <t>-</t>
@@ -33136,7 +33176,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -36240,7 +36280,11 @@
           <t>Depreciation of property and equipment (note 4)</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E412" t="inlineStr">
         <is>
           <t>-</t>
@@ -36302,7 +36346,7 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -40938,7 +40982,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -47270,7 +47318,11 @@
           <t>Depreciation of property and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D562" t="inlineStr"/>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E562" s="5" t="n">
         <v>0.627973</v>
       </c>
@@ -47344,7 +47396,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E563" s="5" t="n">
@@ -47496,7 +47548,11 @@
           <t>Depreciation of property and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D565" t="inlineStr"/>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E565" s="5" t="n">
         <v>0.215447</v>
       </c>
@@ -47570,7 +47626,7 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E566" s="5" t="n">

--- a/output/pdf_financials_xlsx/TC.xlsx
+++ b/output/pdf_financials_xlsx/TC.xlsx
@@ -5337,28 +5337,28 @@
         <v>0.430903</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0.5427380000000001</v>
+        <v>2.431472</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0.526025</v>
+        <v>3.957042</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0.799</v>
+        <v>1.658</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>1.457</v>
+        <v>-1.339</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>2.574</v>
+        <v>1.877</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>2.876</v>
+        <v>2.242</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>3.718</v>
+        <v>2.857</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>7.63</v>
+        <v>6.076</v>
       </c>
       <c r="K107" s="3" t="n">
         <v>7.599</v>
@@ -5730,28 +5730,28 @@
         <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-6.529</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-2.942</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-3.566</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.059</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.782</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.528</v>
       </c>
       <c r="M116" s="3" t="n">
         <v>0</v>
@@ -22390,7 +22390,11 @@
           <t>Deferred income taxes (recovery)</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E217" s="5" t="n">
         <v>-0.247371</v>
       </c>
@@ -22446,7 +22450,11 @@
           <t>Excess tax benefits on share-based compensation expense</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -24810,7 +24818,11 @@
           <t>Acquisition of other intangible assets</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -25454,7 +25466,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -25680,7 +25696,11 @@
           <t>Deferred income taxes (recovery)</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -26800,7 +26820,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -29530,7 +29554,11 @@
           <t>Excess tax benefits from share-based compensation expense</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E318" s="5" t="n">
         <v>1.090171</v>
       </c>
@@ -29752,7 +29780,11 @@
           <t>Acquisition of intangible assets (note 5)</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -29978,7 +30010,11 @@
           <t>Excess tax benefits from share-based compensation expense</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E324" s="5" t="n">
         <v>-1.090171</v>
       </c>
@@ -35838,7 +35874,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
